--- a/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,22</t>
+          <t>0,0; 40,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,85</t>
+          <t>0,0; 49,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,09</t>
+          <t>0,0; 38,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,48</t>
+          <t>0,0; 28,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,05</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 34,08</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 17,7</t>
+          <t>2,01; 17,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 14,57</t>
+          <t>1,76; 15,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 18,98</t>
+          <t>1,97; 18,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,38</t>
+          <t>0,0; 13,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 24,71</t>
+          <t>6,71; 25,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,27</t>
+          <t>2,15; 11,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 16,87</t>
+          <t>5,42; 17,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,41</t>
+          <t>1,77; 10,77</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,56</t>
+          <t>0,0; 40,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 33,78</t>
+          <t>3,94; 32,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 19,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 40,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 52,79</t>
+          <t>6,94; 50,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 30,66</t>
+          <t>3,48; 31,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 21,44</t>
+          <t>2,38; 21,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 23,33</t>
+          <t>2,67; 23,9</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 16,44</t>
+          <t>3,53; 15,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,81</t>
+          <t>3,11; 14,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,5</t>
+          <t>2,23; 13,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,5</t>
+          <t>2,82; 15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 18,66</t>
+          <t>5,23; 18,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,32</t>
+          <t>1,56; 14,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,7</t>
+          <t>3,87; 12,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,81</t>
+          <t>5,16; 13,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,29</t>
+          <t>3,25; 11,17</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2638</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2708</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2745</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3194</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2272</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6077</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>595; 5221</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>618; 5312</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>625; 5871</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3039; 11361</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3527</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1311; 7312</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4352; 14127</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1210; 7346</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2759</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3519</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>638; 5306</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3267</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4005</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>641; 4686</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>643; 5813</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>652; 5794</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>693; 6207</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1551; 6800</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1903; 8644</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1229; 7367</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7394</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3324; 11862</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>748; 6722</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3509; 11239</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6442; 17051</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3348; 11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,09</t>
+          <t>0,0; 39,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,2</t>
+          <t>0,0; 49,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,95</t>
+          <t>0,0; 37,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,63</t>
+          <t>0,0; 24,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 18,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,08</t>
+          <t>0,0; 35,79</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 17,62</t>
+          <t>1,78; 17,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,16</t>
+          <t>1,79; 15,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 18,45</t>
+          <t>1,97; 18,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,43</t>
+          <t>0,0; 13,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 25,08</t>
+          <t>6,64; 25,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 11,99</t>
+          <t>2,36; 12,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 17,58</t>
+          <t>4,92; 16,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,77</t>
+          <t>1,72; 10,29</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,93</t>
+          <t>0,0; 41,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 32,79</t>
+          <t>3,98; 34,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,64</t>
+          <t>0,0; 40,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 50,67</t>
+          <t>7,16; 55,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 31,5</t>
+          <t>3,53; 30,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 21,15</t>
+          <t>2,28; 19,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,9</t>
+          <t>2,81; 24,74</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,5</t>
+          <t>2,65; 15,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,1</t>
+          <t>2,58; 13,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,36</t>
+          <t>3,05; 14,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,83</t>
+          <t>2,83; 14,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,66</t>
+          <t>4,84; 17,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,05</t>
+          <t>1,58; 13,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,41</t>
+          <t>4,04; 12,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,66</t>
+          <t>5,23; 13,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,17</t>
+          <t>3,19; 10,73</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>0; 2622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2745</t>
+          <t>0; 2647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3194</t>
+          <t>0; 2681</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 3242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3006</t>
+          <t>0; 3156</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>595; 5221</t>
+          <t>529; 5113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>618; 5312</t>
+          <t>628; 5393</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>625; 5871</t>
+          <t>627; 5944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 4270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3039; 11361</t>
+          <t>3008; 11536</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3527</t>
+          <t>0; 3343</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1311; 7312</t>
+          <t>1441; 7591</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4352; 14127</t>
+          <t>3956; 13636</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1210; 7346</t>
+          <t>1171; 7017</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3519</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>638; 5306</t>
+          <t>643; 5512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3267</t>
+          <t>0; 2890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 3978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>641; 4686</t>
+          <t>662; 5138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>643; 5813</t>
+          <t>652; 5708</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>652; 5794</t>
+          <t>625; 5415</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>693; 6207</t>
+          <t>730; 6427</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1551; 6800</t>
+          <t>1161; 6945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1903; 8644</t>
+          <t>1579; 8390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1229; 7367</t>
+          <t>1679; 7863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1315; 7394</t>
+          <t>1320; 6767</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3324; 11862</t>
+          <t>3074; 11413</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>748; 6722</t>
+          <t>755; 6453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3509; 11239</t>
+          <t>3659; 11402</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6442; 17051</t>
+          <t>6535; 16554</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3348; 11500</t>
+          <t>3286; 11046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,86%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 48,85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 48,09</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 39,85</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,19</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,03</t>
+          <t>0,0; 24,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,79</t>
+          <t>0,0; 34,39</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 17,26</t>
+          <t>0,0; 16,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,39</t>
+          <t>6,5; 24,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 18,68</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,62</t>
+          <t>2,01; 17,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 25,47</t>
+          <t>1,79; 14,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>2,27; 18,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,45</t>
+          <t>2,07; 12,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 16,97</t>
+          <t>5,27; 16,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,29</t>
+          <t>1,67; 10,41</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,4%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,77</t>
+          <t>0,0; 40,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 34,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>6,92; 52,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,36</t>
+          <t>0,0; 40,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,03; 33,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 55,56</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 30,93</t>
+          <t>3,58; 30,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 19,76</t>
+          <t>2,3; 21,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 24,74</t>
+          <t>2,88; 23,33</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,83</t>
+          <t>2,8; 15,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,69</t>
+          <t>4,42; 18,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,26</t>
+          <t>1,61; 13,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,49</t>
+          <t>3,47; 16,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,96</t>
+          <t>2,43; 14,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,48</t>
+          <t>2,55; 13,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,59</t>
+          <t>4,09; 12,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,26</t>
+          <t>5,33; 13,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,73</t>
+          <t>3,23; 11,29</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 2689</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2622</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2708</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0; 2647</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2681</t>
+          <t>0; 2731</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3242</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3156</t>
+          <t>0; 3033</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6077</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1939</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2499</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6077</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>529; 5113</t>
+          <t>0; 5133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>628; 5393</t>
+          <t>2943; 11194</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>627; 5944</t>
+          <t>0; 3270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4270</t>
+          <t>597; 5244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3008; 11536</t>
+          <t>627; 5106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3343</t>
+          <t>724; 6039</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1441; 7591</t>
+          <t>1265; 7484</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3956; 13636</t>
+          <t>4230; 13557</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1171; 7017</t>
+          <t>1136; 7100</t>
         </is>
       </c>
     </row>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2169</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>597</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3591</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>643; 5512</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2890</t>
+          <t>640; 4882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3978</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>652; 5467</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>662; 5138</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>652; 5708</t>
+          <t>661; 5658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>625; 5415</t>
+          <t>630; 5874</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>730; 6427</t>
+          <t>748; 6060</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4108</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3679</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6684</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1161; 6945</t>
+          <t>1308; 7239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1579; 8390</t>
+          <t>2807; 11859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1679; 7863</t>
+          <t>772; 6375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1320; 6767</t>
+          <t>1525; 7215</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3074; 11413</t>
+          <t>1487; 9075</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>755; 6453</t>
+          <t>1408; 7444</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3659; 11402</t>
+          <t>3704; 11500</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6535; 16554</t>
+          <t>6653; 17248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3286; 11046</t>
+          <t>3330; 11631</t>
         </is>
       </c>
     </row>
